--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/10,26/01,10,26 ПОКОМ ЗПФ/дв 01,10,26 мррсч пок зпф.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/10,26/01,10,26 ПОКОМ ЗПФ/дв 01,10,26 мррсч пок зпф.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\10,26\01,10,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A2109F-E4B7-4477-9999-9F6337C295EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E4D9CA-AF85-4AFF-BE92-C2BA3F146471}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AG$74</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -4194,7 +4194,8 @@
     <col min="30" max="30" width="6" customWidth="1"/>
     <col min="31" max="32" width="5" customWidth="1"/>
     <col min="33" max="33" width="6" style="12" customWidth="1"/>
-    <col min="34" max="52" width="3" customWidth="1"/>
+    <col min="34" max="34" width="8.42578125" customWidth="1"/>
+    <col min="35" max="52" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.25">
@@ -4578,7 +4579,10 @@
         <f>SUM(AG6:AG500)</f>
         <v>19.210317460317462</v>
       </c>
-      <c r="AH5" s="1"/>
+      <c r="AH5" s="4">
+        <f>SUM(AH6:AH500)</f>
+        <v>710.57</v>
+      </c>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
@@ -4668,7 +4672,10 @@
       <c r="AE6" s="14"/>
       <c r="AF6" s="14"/>
       <c r="AG6" s="17"/>
-      <c r="AH6" s="1"/>
+      <c r="AH6" s="1">
+        <f>P6*G6</f>
+        <v>0</v>
+      </c>
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1"/>
@@ -4758,7 +4765,10 @@
       <c r="AE7" s="14"/>
       <c r="AF7" s="14"/>
       <c r="AG7" s="17"/>
-      <c r="AH7" s="1"/>
+      <c r="AH7" s="1">
+        <f t="shared" ref="AH7:AH70" si="5">P7*G7</f>
+        <v>0</v>
+      </c>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
@@ -4871,7 +4881,10 @@
         <f>AC8/AF8</f>
         <v>0</v>
       </c>
-      <c r="AH8" s="1"/>
+      <c r="AH8" s="1">
+        <f t="shared" si="5"/>
+        <v>0.48400000000000004</v>
+      </c>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
@@ -4984,7 +4997,10 @@
         <f>AC9/AF9</f>
         <v>0</v>
       </c>
-      <c r="AH9" s="1"/>
+      <c r="AH9" s="1">
+        <f t="shared" si="5"/>
+        <v>2.88</v>
+      </c>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
@@ -5070,7 +5086,10 @@
       <c r="AE10" s="14"/>
       <c r="AF10" s="14"/>
       <c r="AG10" s="17"/>
-      <c r="AH10" s="1"/>
+      <c r="AH10" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI10" s="1"/>
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
@@ -5158,7 +5177,10 @@
       <c r="AE11" s="14"/>
       <c r="AF11" s="14"/>
       <c r="AG11" s="17"/>
-      <c r="AH11" s="1"/>
+      <c r="AH11" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
@@ -5250,7 +5272,10 @@
       <c r="AE12" s="14"/>
       <c r="AF12" s="14"/>
       <c r="AG12" s="17"/>
-      <c r="AH12" s="1"/>
+      <c r="AH12" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
@@ -5340,7 +5365,10 @@
       <c r="AE13" s="14"/>
       <c r="AF13" s="14"/>
       <c r="AG13" s="17"/>
-      <c r="AH13" s="1"/>
+      <c r="AH13" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
@@ -5409,7 +5437,7 @@
         <v>76</v>
       </c>
       <c r="R14" s="5">
-        <f t="shared" ref="R14" si="5">14*P14-O14-F14</f>
+        <f t="shared" ref="R14" si="6">14*P14-O14-F14</f>
         <v>76</v>
       </c>
       <c r="S14" s="5">
@@ -5458,7 +5486,10 @@
         <f>AC14/AF14</f>
         <v>0.1</v>
       </c>
-      <c r="AH14" s="1"/>
+      <c r="AH14" s="1">
+        <f t="shared" si="5"/>
+        <v>4.7600000000000007</v>
+      </c>
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
@@ -5580,7 +5611,10 @@
         <f>AC15/AF15</f>
         <v>0.8</v>
       </c>
-      <c r="AH15" s="1"/>
+      <c r="AH15" s="1">
+        <f t="shared" si="5"/>
+        <v>3.9359999999999995</v>
+      </c>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
@@ -5672,7 +5706,10 @@
       <c r="AE16" s="14"/>
       <c r="AF16" s="14"/>
       <c r="AG16" s="17"/>
-      <c r="AH16" s="1"/>
+      <c r="AH16" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
@@ -5743,7 +5780,7 @@
         <v>564.80000000000007</v>
       </c>
       <c r="R17" s="5">
-        <f t="shared" ref="R17:R18" si="6">14*P17-O17-F17</f>
+        <f t="shared" ref="R17:R18" si="7">14*P17-O17-F17</f>
         <v>564.80000000000007</v>
       </c>
       <c r="S17" s="5">
@@ -5792,7 +5829,10 @@
         <f>AC17/AF17</f>
         <v>0.6</v>
       </c>
-      <c r="AH17" s="1"/>
+      <c r="AH17" s="1">
+        <f t="shared" si="5"/>
+        <v>13.247999999999999</v>
+      </c>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
@@ -5861,7 +5901,7 @@
         <v>320.40000000000003</v>
       </c>
       <c r="R18" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>320.40000000000003</v>
       </c>
       <c r="S18" s="5">
@@ -5910,7 +5950,10 @@
         <f>AC18/AF18</f>
         <v>0.4</v>
       </c>
-      <c r="AH18" s="1"/>
+      <c r="AH18" s="1">
+        <f t="shared" si="5"/>
+        <v>8.3040000000000003</v>
+      </c>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
@@ -6002,7 +6045,10 @@
       <c r="AE19" s="14"/>
       <c r="AF19" s="14"/>
       <c r="AG19" s="17"/>
-      <c r="AH19" s="1"/>
+      <c r="AH19" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
@@ -6094,7 +6140,10 @@
       <c r="AE20" s="14"/>
       <c r="AF20" s="14"/>
       <c r="AG20" s="17"/>
-      <c r="AH20" s="1"/>
+      <c r="AH20" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI20" s="1"/>
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
@@ -6165,11 +6214,11 @@
         <v>132.40000000000003</v>
       </c>
       <c r="R21" s="5">
-        <f t="shared" ref="R21:R72" si="7">14*P21-O21-F21</f>
+        <f t="shared" ref="R21:R72" si="8">14*P21-O21-F21</f>
         <v>132.40000000000003</v>
       </c>
       <c r="S21" s="5">
-        <f t="shared" ref="S21:S52" si="8">AB21*AC21</f>
+        <f t="shared" ref="S21:S52" si="9">AB21*AC21</f>
         <v>168</v>
       </c>
       <c r="T21" s="23"/>
@@ -6190,18 +6239,18 @@
       </c>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1">
-        <f t="shared" ref="AA21:AA52" si="9">G21*R21</f>
+        <f t="shared" ref="AA21:AA52" si="10">G21*R21</f>
         <v>31.776000000000007</v>
       </c>
       <c r="AB21" s="7">
         <v>12</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" ref="AC21:AC52" si="10">MROUND(R21, AB21*AE21)/AB21</f>
+        <f t="shared" ref="AC21:AC52" si="11">MROUND(R21, AB21*AE21)/AB21</f>
         <v>14</v>
       </c>
       <c r="AD21" s="1">
-        <f t="shared" ref="AD21:AD52" si="11">AC21*AB21*G21</f>
+        <f t="shared" ref="AD21:AD52" si="12">AC21*AB21*G21</f>
         <v>40.32</v>
       </c>
       <c r="AE21" s="1">
@@ -6211,10 +6260,13 @@
         <v>70</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" ref="AG21:AG52" si="12">AC21/AF21</f>
+        <f t="shared" ref="AG21:AG52" si="13">AC21/AF21</f>
         <v>0.2</v>
       </c>
-      <c r="AH21" s="1"/>
+      <c r="AH21" s="1">
+        <f t="shared" si="5"/>
+        <v>8.0640000000000001</v>
+      </c>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
@@ -6278,7 +6330,7 @@
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
       <c r="S22" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T22" s="23"/>
@@ -6299,20 +6351,20 @@
       </c>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AB22" s="7">
         <v>8</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AD22" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
+      <c r="AD22" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="AE22" s="1">
         <v>14</v>
       </c>
@@ -6320,10 +6372,13 @@
         <v>70</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AH22" s="1"/>
+      <c r="AH22" s="1">
+        <f t="shared" si="5"/>
+        <v>3.6479999999999997</v>
+      </c>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
@@ -6396,7 +6451,7 @@
         <v>400</v>
       </c>
       <c r="S23" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>336</v>
       </c>
       <c r="T23" s="23">
@@ -6423,18 +6478,18 @@
       </c>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
       <c r="AB23" s="7">
         <v>24</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
       <c r="AD23" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>30.24</v>
       </c>
       <c r="AE23" s="1">
@@ -6444,10 +6499,13 @@
         <v>126</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="AH23" s="1"/>
+      <c r="AH23" s="1">
+        <f t="shared" si="5"/>
+        <v>3.528</v>
+      </c>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
@@ -6517,7 +6575,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T24" s="23"/>
@@ -6540,20 +6598,20 @@
         <v>71</v>
       </c>
       <c r="AA24" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AB24" s="7">
         <v>10</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AD24" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
+      <c r="AD24" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="AE24" s="1">
         <v>14</v>
       </c>
@@ -6561,10 +6619,13 @@
         <v>70</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AH24" s="1"/>
+      <c r="AH24" s="1">
+        <f t="shared" si="5"/>
+        <v>0.64800000000000002</v>
+      </c>
       <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
@@ -6632,7 +6693,7 @@
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
       <c r="S25" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T25" s="23"/>
@@ -6653,20 +6714,20 @@
       </c>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AB25" s="7">
         <v>12</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AD25" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
+      <c r="AD25" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="AE25" s="1">
         <v>14</v>
       </c>
@@ -6674,10 +6735,13 @@
         <v>70</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AH25" s="1"/>
+      <c r="AH25" s="1">
+        <f t="shared" si="5"/>
+        <v>0.91999999999999993</v>
+      </c>
       <c r="AI25" s="1"/>
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
@@ -6746,11 +6810,11 @@
         <v>374.4</v>
       </c>
       <c r="R26" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>374.4</v>
       </c>
       <c r="S26" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>336</v>
       </c>
       <c r="T26" s="23"/>
@@ -6771,18 +6835,18 @@
       </c>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>74.88</v>
       </c>
       <c r="AB26" s="7">
         <v>12</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>28</v>
       </c>
       <c r="AD26" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>67.2</v>
       </c>
       <c r="AE26" s="1">
@@ -6792,10 +6856,13 @@
         <v>70</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.4</v>
       </c>
-      <c r="AH26" s="1"/>
+      <c r="AH26" s="1">
+        <f t="shared" si="5"/>
+        <v>12.520000000000001</v>
+      </c>
       <c r="AI26" s="1"/>
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
@@ -6864,11 +6931,11 @@
       </c>
       <c r="Q27" s="5"/>
       <c r="R27" s="5">
-        <f t="shared" ref="R27:R28" si="13">T27</f>
+        <f t="shared" ref="R27:R28" si="14">T27</f>
         <v>1100</v>
       </c>
       <c r="S27" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1176</v>
       </c>
       <c r="T27" s="23">
@@ -6895,18 +6962,18 @@
       </c>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>220</v>
       </c>
       <c r="AB27" s="7">
         <v>12</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AD27" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>235.20000000000002</v>
       </c>
       <c r="AE27" s="1">
@@ -6916,10 +6983,13 @@
         <v>70</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.4</v>
       </c>
-      <c r="AH27" s="1"/>
+      <c r="AH27" s="1">
+        <f t="shared" si="5"/>
+        <v>2.3199999999999998</v>
+      </c>
       <c r="AI27" s="1"/>
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
@@ -6986,11 +7056,11 @@
       </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>200</v>
       </c>
       <c r="S28" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>207.20000000000002</v>
       </c>
       <c r="T28" s="23">
@@ -7017,18 +7087,18 @@
       </c>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>200</v>
       </c>
       <c r="AB28" s="7">
         <v>3.7</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>56</v>
       </c>
       <c r="AD28" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>207.20000000000002</v>
       </c>
       <c r="AE28" s="1">
@@ -7038,10 +7108,13 @@
         <v>126</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.44444444444444442</v>
       </c>
-      <c r="AH28" s="1"/>
+      <c r="AH28" s="1">
+        <f t="shared" si="5"/>
+        <v>2.82</v>
+      </c>
       <c r="AI28" s="1"/>
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
@@ -7109,7 +7182,7 @@
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
       <c r="S29" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T29" s="23"/>
@@ -7130,20 +7203,20 @@
       </c>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AB29" s="7">
         <v>3</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AD29" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
+      <c r="AD29" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="AE29" s="1">
         <v>14</v>
       </c>
@@ -7151,10 +7224,13 @@
         <v>126</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="1"/>
+      <c r="AH29" s="1">
+        <f t="shared" si="5"/>
+        <v>2.4</v>
+      </c>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1"/>
@@ -7229,7 +7305,7 @@
         <v>1000</v>
       </c>
       <c r="S30" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1008</v>
       </c>
       <c r="T30" s="23">
@@ -7256,18 +7332,18 @@
       </c>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>250</v>
       </c>
       <c r="AB30" s="7">
         <v>6</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>168</v>
       </c>
       <c r="AD30" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>252</v>
       </c>
       <c r="AE30" s="1">
@@ -7277,10 +7353,13 @@
         <v>140</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.2</v>
       </c>
-      <c r="AH30" s="1"/>
+      <c r="AH30" s="1">
+        <f t="shared" si="5"/>
+        <v>20.149999999999999</v>
+      </c>
       <c r="AI30" s="1"/>
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
@@ -7340,7 +7419,7 @@
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
       <c r="S31" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T31" s="23"/>
@@ -7361,20 +7440,20 @@
       </c>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AB31" s="7">
         <v>6</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AD31" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
+      <c r="AD31" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="AE31" s="1">
         <v>14</v>
       </c>
@@ -7382,10 +7461,13 @@
         <v>140</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AH31" s="1"/>
+      <c r="AH31" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
@@ -7451,7 +7533,7 @@
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
       <c r="S32" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T32" s="23"/>
@@ -7472,20 +7554,20 @@
       </c>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AB32" s="7">
         <v>6</v>
       </c>
       <c r="AC32" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AD32" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
+      <c r="AD32" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="AE32" s="1">
         <v>12</v>
       </c>
@@ -7493,10 +7575,13 @@
         <v>84</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AH32" s="1"/>
+      <c r="AH32" s="1">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
       <c r="AI32" s="1"/>
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
@@ -7563,11 +7648,11 @@
       </c>
       <c r="Q33" s="5"/>
       <c r="R33" s="5">
-        <f t="shared" ref="R33:R37" si="14">T33</f>
+        <f t="shared" ref="R33:R37" si="15">T33</f>
         <v>210</v>
       </c>
       <c r="S33" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>168</v>
       </c>
       <c r="T33" s="23">
@@ -7594,18 +7679,18 @@
       </c>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>48.300000000000004</v>
       </c>
       <c r="AB33" s="7">
         <v>12</v>
       </c>
       <c r="AC33" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
       <c r="AD33" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>38.64</v>
       </c>
       <c r="AE33" s="1">
@@ -7615,10 +7700,13 @@
         <v>70</v>
       </c>
       <c r="AG33" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.2</v>
       </c>
-      <c r="AH33" s="1"/>
+      <c r="AH33" s="1">
+        <f t="shared" si="5"/>
+        <v>2.2080000000000002</v>
+      </c>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
@@ -7687,11 +7775,11 @@
         <v>190</v>
       </c>
       <c r="R34" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>500</v>
       </c>
       <c r="S34" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>504</v>
       </c>
       <c r="T34" s="23">
@@ -7718,18 +7806,18 @@
       </c>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>125</v>
       </c>
       <c r="AB34" s="7">
         <v>12</v>
       </c>
       <c r="AC34" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>42</v>
       </c>
       <c r="AD34" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>126</v>
       </c>
       <c r="AE34" s="1">
@@ -7739,10 +7827,13 @@
         <v>70</v>
       </c>
       <c r="AG34" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.6</v>
       </c>
-      <c r="AH34" s="1"/>
+      <c r="AH34" s="1">
+        <f t="shared" si="5"/>
+        <v>7.75</v>
+      </c>
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
@@ -7811,11 +7902,11 @@
         <v>250.19999999999993</v>
       </c>
       <c r="R35" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>300</v>
       </c>
       <c r="S35" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>336</v>
       </c>
       <c r="T35" s="23">
@@ -7842,18 +7933,18 @@
       </c>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>75</v>
       </c>
       <c r="AB35" s="7">
         <v>12</v>
       </c>
       <c r="AC35" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>28</v>
       </c>
       <c r="AD35" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="AE35" s="1">
@@ -7863,10 +7954,13 @@
         <v>70</v>
       </c>
       <c r="AG35" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.4</v>
       </c>
-      <c r="AH35" s="1"/>
+      <c r="AH35" s="1">
+        <f t="shared" si="5"/>
+        <v>9.4499999999999993</v>
+      </c>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
@@ -7935,11 +8029,11 @@
         <v>188.59999999999997</v>
       </c>
       <c r="R36" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>400</v>
       </c>
       <c r="S36" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>336</v>
       </c>
       <c r="T36" s="23">
@@ -7966,18 +8060,18 @@
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>100</v>
       </c>
       <c r="AB36" s="7">
         <v>12</v>
       </c>
       <c r="AC36" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>28</v>
       </c>
       <c r="AD36" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="AE36" s="1">
@@ -7987,10 +8081,13 @@
         <v>70</v>
       </c>
       <c r="AG36" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.4</v>
       </c>
-      <c r="AH36" s="1"/>
+      <c r="AH36" s="1">
+        <f t="shared" si="5"/>
+        <v>7.35</v>
+      </c>
       <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
@@ -8055,11 +8152,11 @@
         <v>89.400000000000034</v>
       </c>
       <c r="R37" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>300</v>
       </c>
       <c r="S37" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>336</v>
       </c>
       <c r="T37" s="23">
@@ -8086,18 +8183,18 @@
       </c>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>75</v>
       </c>
       <c r="AB37" s="7">
         <v>12</v>
       </c>
       <c r="AC37" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>28</v>
       </c>
       <c r="AD37" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="AE37" s="1">
@@ -8107,10 +8204,13 @@
         <v>70</v>
       </c>
       <c r="AG37" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.4</v>
       </c>
-      <c r="AH37" s="1"/>
+      <c r="AH37" s="1">
+        <f t="shared" si="5"/>
+        <v>5.4</v>
+      </c>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
@@ -8163,7 +8263,7 @@
         <v>123</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="15">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="16">E38-K38</f>
         <v>22</v>
       </c>
       <c r="M38" s="1"/>
@@ -8172,28 +8272,28 @@
         <v>192</v>
       </c>
       <c r="P38" s="1">
-        <f t="shared" ref="P38:P74" si="16">E38/5</f>
+        <f t="shared" ref="P38:P74" si="17">E38/5</f>
         <v>29</v>
       </c>
       <c r="Q38" s="5">
         <v>193</v>
       </c>
       <c r="R38" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>193</v>
       </c>
       <c r="S38" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>192</v>
       </c>
       <c r="T38" s="23"/>
       <c r="U38" s="23"/>
       <c r="V38" s="1">
-        <f t="shared" ref="V38:V69" si="17">(F38+O38+S38)/P38</f>
+        <f t="shared" ref="V38:V69" si="18">(F38+O38+S38)/P38</f>
         <v>13.96551724137931</v>
       </c>
       <c r="W38" s="1">
-        <f t="shared" ref="W38:W74" si="18">(F38+O38)/P38</f>
+        <f t="shared" ref="W38:W74" si="19">(F38+O38)/P38</f>
         <v>7.3448275862068968</v>
       </c>
       <c r="X38" s="1">
@@ -8204,18 +8304,18 @@
       </c>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>135.1</v>
       </c>
       <c r="AB38" s="7">
         <v>8</v>
       </c>
       <c r="AC38" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>24</v>
       </c>
       <c r="AD38" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>134.39999999999998</v>
       </c>
       <c r="AE38" s="1">
@@ -8225,10 +8325,13 @@
         <v>84</v>
       </c>
       <c r="AG38" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AH38" s="1"/>
+      <c r="AH38" s="1">
+        <f t="shared" si="5"/>
+        <v>20.299999999999997</v>
+      </c>
       <c r="AI38" s="1"/>
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
@@ -8281,7 +8384,7 @@
         <v>103</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-25</v>
       </c>
       <c r="M39" s="1"/>
@@ -8290,7 +8393,7 @@
         <v>192</v>
       </c>
       <c r="P39" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>15.6</v>
       </c>
       <c r="Q39" s="5">
@@ -8301,17 +8404,17 @@
         <v>59.599999999999994</v>
       </c>
       <c r="S39" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>96</v>
       </c>
       <c r="T39" s="23"/>
       <c r="U39" s="23"/>
       <c r="V39" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>18.333333333333332</v>
       </c>
       <c r="W39" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12.179487179487181</v>
       </c>
       <c r="X39" s="1">
@@ -8322,18 +8425,18 @@
       </c>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>41.719999999999992</v>
       </c>
       <c r="AB39" s="7">
         <v>8</v>
       </c>
       <c r="AC39" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="AD39" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>67.199999999999989</v>
       </c>
       <c r="AE39" s="1">
@@ -8343,10 +8446,13 @@
         <v>84</v>
       </c>
       <c r="AG39" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AH39" s="1"/>
+      <c r="AH39" s="1">
+        <f t="shared" si="5"/>
+        <v>10.92</v>
+      </c>
       <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
@@ -8391,7 +8497,7 @@
         <v>104</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-104</v>
       </c>
       <c r="M40" s="1"/>
@@ -8400,7 +8506,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Q40" s="22">
@@ -8410,19 +8516,19 @@
         <v>0</v>
       </c>
       <c r="S40" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T40" s="23"/>
       <c r="U40" s="23"/>
       <c r="V40" s="1" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W40" s="1" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="W40" s="1" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X40" s="1">
         <v>0</v>
       </c>
@@ -8433,20 +8539,20 @@
         <v>71</v>
       </c>
       <c r="AA40" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AB40" s="7">
         <v>8</v>
       </c>
       <c r="AC40" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AD40" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
+      <c r="AD40" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="AE40" s="1">
         <v>12</v>
       </c>
@@ -8454,10 +8560,13 @@
         <v>84</v>
       </c>
       <c r="AG40" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AH40" s="1"/>
+      <c r="AH40" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI40" s="1"/>
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
@@ -8510,7 +8619,7 @@
         <v>222</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-8</v>
       </c>
       <c r="M41" s="1"/>
@@ -8519,28 +8628,28 @@
         <v>360</v>
       </c>
       <c r="P41" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>42.8</v>
       </c>
       <c r="Q41" s="5">
         <v>231.19999999999993</v>
       </c>
       <c r="R41" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>231.19999999999993</v>
       </c>
       <c r="S41" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>240</v>
       </c>
       <c r="T41" s="23"/>
       <c r="U41" s="23"/>
       <c r="V41" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>14.205607476635516</v>
       </c>
       <c r="W41" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>8.5981308411214954</v>
       </c>
       <c r="X41" s="1">
@@ -8551,18 +8660,18 @@
       </c>
       <c r="Z41" s="1"/>
       <c r="AA41" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>161.83999999999995</v>
       </c>
       <c r="AB41" s="7">
         <v>10</v>
       </c>
       <c r="AC41" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>24</v>
       </c>
       <c r="AD41" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>168</v>
       </c>
       <c r="AE41" s="1">
@@ -8572,10 +8681,13 @@
         <v>84</v>
       </c>
       <c r="AG41" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AH41" s="1"/>
+      <c r="AH41" s="1">
+        <f t="shared" si="5"/>
+        <v>29.959999999999997</v>
+      </c>
       <c r="AI41" s="1"/>
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
@@ -8628,7 +8740,7 @@
         <v>240</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-4</v>
       </c>
       <c r="M42" s="1"/>
@@ -8637,28 +8749,28 @@
         <v>360</v>
       </c>
       <c r="P42" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>47.2</v>
       </c>
       <c r="Q42" s="5">
         <v>302.80000000000007</v>
       </c>
       <c r="R42" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>302.80000000000007</v>
       </c>
       <c r="S42" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>360</v>
       </c>
       <c r="T42" s="23"/>
       <c r="U42" s="23"/>
       <c r="V42" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>15.211864406779661</v>
       </c>
       <c r="W42" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.5847457627118642</v>
       </c>
       <c r="X42" s="1">
@@ -8669,18 +8781,18 @@
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>211.96000000000004</v>
       </c>
       <c r="AB42" s="7">
         <v>10</v>
       </c>
       <c r="AC42" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>36</v>
       </c>
       <c r="AD42" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>251.99999999999997</v>
       </c>
       <c r="AE42" s="1">
@@ -8690,10 +8802,13 @@
         <v>84</v>
       </c>
       <c r="AG42" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="AH42" s="1"/>
+      <c r="AH42" s="1">
+        <f t="shared" si="5"/>
+        <v>33.04</v>
+      </c>
       <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
@@ -8746,7 +8861,7 @@
         <v>260</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M43" s="1"/>
@@ -8755,28 +8870,28 @@
         <v>360</v>
       </c>
       <c r="P43" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>56</v>
       </c>
       <c r="Q43" s="5">
         <v>250</v>
       </c>
       <c r="R43" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>250</v>
       </c>
       <c r="S43" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>240</v>
       </c>
       <c r="T43" s="23"/>
       <c r="U43" s="23"/>
       <c r="V43" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>13.821428571428571</v>
       </c>
       <c r="W43" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9.5357142857142865</v>
       </c>
       <c r="X43" s="1">
@@ -8787,18 +8902,18 @@
       </c>
       <c r="Z43" s="1"/>
       <c r="AA43" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>175</v>
       </c>
       <c r="AB43" s="7">
         <v>10</v>
       </c>
       <c r="AC43" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>24</v>
       </c>
       <c r="AD43" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>168</v>
       </c>
       <c r="AE43" s="1">
@@ -8808,10 +8923,13 @@
         <v>84</v>
       </c>
       <c r="AG43" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AH43" s="1"/>
+      <c r="AH43" s="1">
+        <f t="shared" si="5"/>
+        <v>39.199999999999996</v>
+      </c>
       <c r="AI43" s="1"/>
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
@@ -8862,7 +8980,7 @@
         <v>73</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-15</v>
       </c>
       <c r="M44" s="1"/>
@@ -8871,7 +8989,7 @@
         <v>120</v>
       </c>
       <c r="P44" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11.6</v>
       </c>
       <c r="Q44" s="5">
@@ -8882,7 +9000,7 @@
         <v>160</v>
       </c>
       <c r="S44" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>120</v>
       </c>
       <c r="T44" s="23">
@@ -8894,11 +9012,11 @@
         <v>Сети</v>
       </c>
       <c r="V44" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>20.689655172413794</v>
       </c>
       <c r="W44" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10.344827586206897</v>
       </c>
       <c r="X44" s="1">
@@ -8909,18 +9027,18 @@
       </c>
       <c r="Z44" s="1"/>
       <c r="AA44" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>112</v>
       </c>
       <c r="AB44" s="7">
         <v>10</v>
       </c>
       <c r="AC44" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="AD44" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="AE44" s="1">
@@ -8930,10 +9048,13 @@
         <v>84</v>
       </c>
       <c r="AG44" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AH44" s="1"/>
+      <c r="AH44" s="1">
+        <f t="shared" si="5"/>
+        <v>8.1199999999999992</v>
+      </c>
       <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
       <c r="AK44" s="1"/>
@@ -8986,7 +9107,7 @@
         <v>585</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>275</v>
       </c>
       <c r="M45" s="1"/>
@@ -8995,28 +9116,28 @@
         <v>1080</v>
       </c>
       <c r="P45" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>172</v>
       </c>
       <c r="Q45" s="5">
         <v>1303</v>
       </c>
       <c r="R45" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1303</v>
       </c>
       <c r="S45" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1320</v>
       </c>
       <c r="T45" s="23"/>
       <c r="U45" s="23"/>
       <c r="V45" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>14.098837209302326</v>
       </c>
       <c r="W45" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6.4244186046511631</v>
       </c>
       <c r="X45" s="1">
@@ -9027,18 +9148,18 @@
       </c>
       <c r="Z45" s="1"/>
       <c r="AA45" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1303</v>
       </c>
       <c r="AB45" s="7">
         <v>5</v>
       </c>
       <c r="AC45" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>264</v>
       </c>
       <c r="AD45" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1320</v>
       </c>
       <c r="AE45" s="1">
@@ -9048,10 +9169,13 @@
         <v>144</v>
       </c>
       <c r="AG45" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.8333333333333333</v>
       </c>
-      <c r="AH45" s="1"/>
+      <c r="AH45" s="1">
+        <f t="shared" si="5"/>
+        <v>172</v>
+      </c>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
@@ -9102,7 +9226,7 @@
         <v>236</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-161</v>
       </c>
       <c r="M46" s="1"/>
@@ -9111,7 +9235,7 @@
         <v>192</v>
       </c>
       <c r="P46" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>15</v>
       </c>
       <c r="Q46" s="5">
@@ -9122,17 +9246,17 @@
         <v>108</v>
       </c>
       <c r="S46" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>192</v>
       </c>
       <c r="T46" s="23"/>
       <c r="U46" s="23"/>
       <c r="V46" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>25.6</v>
       </c>
       <c r="W46" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12.8</v>
       </c>
       <c r="X46" s="1">
@@ -9143,18 +9267,18 @@
       </c>
       <c r="Z46" s="1"/>
       <c r="AA46" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>43.2</v>
       </c>
       <c r="AB46" s="7">
         <v>16</v>
       </c>
       <c r="AC46" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="AD46" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>76.800000000000011</v>
       </c>
       <c r="AE46" s="1">
@@ -9164,10 +9288,13 @@
         <v>84</v>
       </c>
       <c r="AG46" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AH46" s="1"/>
+      <c r="AH46" s="1">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
       <c r="AI46" s="1"/>
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
@@ -9220,7 +9347,7 @@
         <v>379</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-40</v>
       </c>
       <c r="M47" s="1"/>
@@ -9229,28 +9356,28 @@
         <v>480</v>
       </c>
       <c r="P47" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>67.8</v>
       </c>
       <c r="Q47" s="5">
         <v>460.19999999999993</v>
       </c>
       <c r="R47" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>460.19999999999993</v>
       </c>
       <c r="S47" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>480</v>
       </c>
       <c r="T47" s="23"/>
       <c r="U47" s="23"/>
       <c r="V47" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>14.292035398230089</v>
       </c>
       <c r="W47" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.2123893805309738</v>
       </c>
       <c r="X47" s="1">
@@ -9261,18 +9388,18 @@
       </c>
       <c r="Z47" s="1"/>
       <c r="AA47" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>322.13999999999993</v>
       </c>
       <c r="AB47" s="7">
         <v>10</v>
       </c>
       <c r="AC47" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>48</v>
       </c>
       <c r="AD47" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>336</v>
       </c>
       <c r="AE47" s="1">
@@ -9282,10 +9409,13 @@
         <v>84</v>
       </c>
       <c r="AG47" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="AH47" s="1"/>
+      <c r="AH47" s="1">
+        <f t="shared" si="5"/>
+        <v>47.459999999999994</v>
+      </c>
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
@@ -9338,7 +9468,7 @@
         <v>234</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-189</v>
       </c>
       <c r="M48" s="1"/>
@@ -9347,7 +9477,7 @@
         <v>192</v>
       </c>
       <c r="P48" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>9</v>
       </c>
       <c r="Q48" s="5"/>
@@ -9356,7 +9486,7 @@
         <v>250</v>
       </c>
       <c r="S48" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>192</v>
       </c>
       <c r="T48" s="23">
@@ -9368,11 +9498,11 @@
         <v>Сети</v>
       </c>
       <c r="V48" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>42.555555555555557</v>
       </c>
       <c r="W48" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>21.222222222222221</v>
       </c>
       <c r="X48" s="1">
@@ -9383,18 +9513,18 @@
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>100</v>
       </c>
       <c r="AB48" s="7">
         <v>16</v>
       </c>
       <c r="AC48" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="AD48" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>76.800000000000011</v>
       </c>
       <c r="AE48" s="1">
@@ -9404,10 +9534,13 @@
         <v>84</v>
       </c>
       <c r="AG48" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AH48" s="1"/>
+      <c r="AH48" s="1">
+        <f t="shared" si="5"/>
+        <v>3.6</v>
+      </c>
       <c r="AI48" s="1"/>
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
@@ -9460,7 +9593,7 @@
         <v>444</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-24</v>
       </c>
       <c r="M49" s="1"/>
@@ -9469,28 +9602,28 @@
         <v>600</v>
       </c>
       <c r="P49" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="Q49" s="5">
         <v>565</v>
       </c>
       <c r="R49" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>565</v>
       </c>
       <c r="S49" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>600</v>
       </c>
       <c r="T49" s="23"/>
       <c r="U49" s="23"/>
       <c r="V49" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>14.416666666666666</v>
       </c>
       <c r="W49" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.2738095238095237</v>
       </c>
       <c r="X49" s="1">
@@ -9501,18 +9634,18 @@
       </c>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>395.5</v>
       </c>
       <c r="AB49" s="7">
         <v>10</v>
       </c>
       <c r="AC49" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>60</v>
       </c>
       <c r="AD49" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>420</v>
       </c>
       <c r="AE49" s="1">
@@ -9522,10 +9655,13 @@
         <v>84</v>
       </c>
       <c r="AG49" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.7142857142857143</v>
       </c>
-      <c r="AH49" s="1"/>
+      <c r="AH49" s="1">
+        <f t="shared" si="5"/>
+        <v>58.8</v>
+      </c>
       <c r="AI49" s="1"/>
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
@@ -9570,7 +9706,7 @@
         <v>10</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-10</v>
       </c>
       <c r="M50" s="1"/>
@@ -9579,25 +9715,25 @@
         <v>120</v>
       </c>
       <c r="P50" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Q50" s="5"/>
       <c r="R50" s="5"/>
       <c r="S50" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T50" s="23"/>
       <c r="U50" s="23"/>
       <c r="V50" s="1" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W50" s="1" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="W50" s="1" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X50" s="1">
         <v>0</v>
       </c>
@@ -9606,20 +9742,20 @@
       </c>
       <c r="Z50" s="1"/>
       <c r="AA50" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AB50" s="7">
         <v>10</v>
       </c>
       <c r="AC50" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AD50" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
+      <c r="AD50" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="AE50" s="1">
         <v>12</v>
       </c>
@@ -9627,10 +9763,13 @@
         <v>84</v>
       </c>
       <c r="AG50" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AH50" s="1"/>
+      <c r="AH50" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI50" s="1"/>
       <c r="AJ50" s="1"/>
       <c r="AK50" s="1"/>
@@ -9679,7 +9818,7 @@
         <v>19</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-19</v>
       </c>
       <c r="M51" s="1"/>
@@ -9688,7 +9827,7 @@
         <v>288</v>
       </c>
       <c r="P51" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Q51" s="5"/>
@@ -9697,7 +9836,7 @@
         <v>350</v>
       </c>
       <c r="S51" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>384</v>
       </c>
       <c r="T51" s="23">
@@ -9709,13 +9848,13 @@
         <v>Промо Октябрь</v>
       </c>
       <c r="V51" s="1" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W51" s="1" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="W51" s="1" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X51" s="1">
         <v>0</v>
       </c>
@@ -9724,18 +9863,18 @@
       </c>
       <c r="Z51" s="1"/>
       <c r="AA51" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>280</v>
       </c>
       <c r="AB51" s="7">
         <v>8</v>
       </c>
       <c r="AC51" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>48</v>
       </c>
       <c r="AD51" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>307.20000000000005</v>
       </c>
       <c r="AE51" s="1">
@@ -9745,10 +9884,13 @@
         <v>84</v>
       </c>
       <c r="AG51" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="AH51" s="1"/>
+      <c r="AH51" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI51" s="1"/>
       <c r="AJ51" s="1"/>
       <c r="AK51" s="1"/>
@@ -9801,7 +9943,7 @@
         <v>115</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-25</v>
       </c>
       <c r="M52" s="1"/>
@@ -9810,28 +9952,28 @@
         <v>120</v>
       </c>
       <c r="P52" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>18</v>
       </c>
       <c r="Q52" s="5">
         <v>126</v>
       </c>
       <c r="R52" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>126</v>
       </c>
       <c r="S52" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>120</v>
       </c>
       <c r="T52" s="23"/>
       <c r="U52" s="23"/>
       <c r="V52" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>13.666666666666666</v>
       </c>
       <c r="W52" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7</v>
       </c>
       <c r="X52" s="1">
@@ -9842,18 +9984,18 @@
       </c>
       <c r="Z52" s="1"/>
       <c r="AA52" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>126</v>
       </c>
       <c r="AB52" s="7">
         <v>5</v>
       </c>
       <c r="AC52" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>24</v>
       </c>
       <c r="AD52" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>120</v>
       </c>
       <c r="AE52" s="1">
@@ -9863,10 +10005,13 @@
         <v>84</v>
       </c>
       <c r="AG52" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AH52" s="1"/>
+      <c r="AH52" s="1">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
       <c r="AI52" s="1"/>
       <c r="AJ52" s="1"/>
       <c r="AK52" s="1"/>
@@ -9915,7 +10060,7 @@
         <v>4</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-4</v>
       </c>
       <c r="M53" s="1"/>
@@ -9924,25 +10069,25 @@
         <v>96</v>
       </c>
       <c r="P53" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Q53" s="5"/>
       <c r="R53" s="5"/>
       <c r="S53" s="5">
-        <f t="shared" ref="S53:S74" si="19">AB53*AC53</f>
+        <f t="shared" ref="S53:S74" si="20">AB53*AC53</f>
         <v>0</v>
       </c>
       <c r="T53" s="23"/>
       <c r="U53" s="23"/>
       <c r="V53" s="1" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W53" s="1" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="W53" s="1" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X53" s="1">
         <v>0</v>
       </c>
@@ -9951,18 +10096,18 @@
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1">
-        <f t="shared" ref="AA53:AA74" si="20">G53*R53</f>
+        <f t="shared" ref="AA53:AA74" si="21">G53*R53</f>
         <v>0</v>
       </c>
       <c r="AB53" s="7">
         <v>8</v>
       </c>
       <c r="AC53" s="9">
-        <f t="shared" ref="AC53:AC74" si="21">MROUND(R53, AB53*AE53)/AB53</f>
+        <f t="shared" ref="AC53:AC74" si="22">MROUND(R53, AB53*AE53)/AB53</f>
         <v>0</v>
       </c>
       <c r="AD53" s="1">
-        <f t="shared" ref="AD53:AD74" si="22">AC53*AB53*G53</f>
+        <f t="shared" ref="AD53:AD74" si="23">AC53*AB53*G53</f>
         <v>0</v>
       </c>
       <c r="AE53" s="1">
@@ -9972,10 +10117,13 @@
         <v>84</v>
       </c>
       <c r="AG53" s="9">
-        <f t="shared" ref="AG53:AG74" si="23">AC53/AF53</f>
+        <f t="shared" ref="AG53:AG74" si="24">AC53/AF53</f>
         <v>0</v>
       </c>
-      <c r="AH53" s="1"/>
+      <c r="AH53" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI53" s="1"/>
       <c r="AJ53" s="1"/>
       <c r="AK53" s="1"/>
@@ -10028,7 +10176,7 @@
         <v>36</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-19</v>
       </c>
       <c r="M54" s="1"/>
@@ -10037,25 +10185,25 @@
         <v>96</v>
       </c>
       <c r="P54" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>3.4</v>
       </c>
       <c r="Q54" s="5"/>
       <c r="R54" s="5"/>
       <c r="S54" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="T54" s="23"/>
       <c r="U54" s="23"/>
       <c r="V54" s="1">
-        <f t="shared" si="17"/>
-        <v>30.882352941176471</v>
-      </c>
-      <c r="W54" s="1">
         <f t="shared" si="18"/>
         <v>30.882352941176471</v>
       </c>
+      <c r="W54" s="1">
+        <f t="shared" si="19"/>
+        <v>30.882352941176471</v>
+      </c>
       <c r="X54" s="1">
         <v>3.8</v>
       </c>
@@ -10064,20 +10212,20 @@
       </c>
       <c r="Z54" s="1"/>
       <c r="AA54" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AB54" s="7">
         <v>8</v>
       </c>
       <c r="AC54" s="9">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AD54" s="1">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AD54" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AE54" s="1">
         <v>12</v>
       </c>
@@ -10085,10 +10233,13 @@
         <v>84</v>
       </c>
       <c r="AG54" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AH54" s="1"/>
+      <c r="AH54" s="1">
+        <f t="shared" si="5"/>
+        <v>3.06</v>
+      </c>
       <c r="AI54" s="1"/>
       <c r="AJ54" s="1"/>
       <c r="AK54" s="1"/>
@@ -10137,7 +10288,7 @@
         <v>25</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-10</v>
       </c>
       <c r="M55" s="1"/>
@@ -10146,16 +10297,16 @@
         <v>180</v>
       </c>
       <c r="P55" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="Q55" s="5"/>
       <c r="R55" s="5">
-        <f t="shared" ref="R55:R56" si="24">T55</f>
+        <f t="shared" ref="R55:R56" si="25">T55</f>
         <v>150</v>
       </c>
       <c r="S55" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>180</v>
       </c>
       <c r="T55" s="23">
@@ -10167,11 +10318,11 @@
         <v>Есть спрос</v>
       </c>
       <c r="V55" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>113.33333333333333</v>
       </c>
       <c r="W55" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>53.333333333333336</v>
       </c>
       <c r="X55" s="1">
@@ -10182,18 +10333,18 @@
       </c>
       <c r="Z55" s="1"/>
       <c r="AA55" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>150</v>
       </c>
       <c r="AB55" s="7">
         <v>5</v>
       </c>
       <c r="AC55" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>36</v>
       </c>
       <c r="AD55" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>180</v>
       </c>
       <c r="AE55" s="1">
@@ -10203,10 +10354,13 @@
         <v>144</v>
       </c>
       <c r="AG55" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.25</v>
       </c>
-      <c r="AH55" s="1"/>
+      <c r="AH55" s="1">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
       <c r="AI55" s="1"/>
       <c r="AJ55" s="1"/>
       <c r="AK55" s="1"/>
@@ -10249,7 +10403,7 @@
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M56" s="1"/>
@@ -10258,16 +10412,16 @@
         <v>240</v>
       </c>
       <c r="P56" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Q56" s="5"/>
       <c r="R56" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>250</v>
       </c>
       <c r="S56" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>240</v>
       </c>
       <c r="T56" s="23">
@@ -10279,13 +10433,13 @@
         <v>Промо Октябрь</v>
       </c>
       <c r="V56" s="1" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W56" s="1" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="W56" s="1" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X56" s="1">
         <v>0</v>
       </c>
@@ -10294,18 +10448,18 @@
       </c>
       <c r="Z56" s="1"/>
       <c r="AA56" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>250</v>
       </c>
       <c r="AB56" s="7">
         <v>5</v>
       </c>
       <c r="AC56" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>48</v>
       </c>
       <c r="AD56" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>240</v>
       </c>
       <c r="AE56" s="1">
@@ -10315,10 +10469,13 @@
         <v>84</v>
       </c>
       <c r="AG56" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="AH56" s="1"/>
+      <c r="AH56" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI56" s="1"/>
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
@@ -10369,7 +10526,7 @@
         <v>3.7</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-3.7</v>
       </c>
       <c r="M57" s="1"/>
@@ -10378,25 +10535,25 @@
         <v>0</v>
       </c>
       <c r="P57" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Q57" s="5"/>
       <c r="R57" s="5"/>
       <c r="S57" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="T57" s="23"/>
       <c r="U57" s="23"/>
       <c r="V57" s="1" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W57" s="1" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="W57" s="1" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X57" s="1">
         <v>0</v>
       </c>
@@ -10407,20 +10564,20 @@
         <v>167</v>
       </c>
       <c r="AA57" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AB57" s="7">
         <v>3.7</v>
       </c>
       <c r="AC57" s="9">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AD57" s="1">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AD57" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AE57" s="1">
         <v>14</v>
       </c>
@@ -10428,10 +10585,13 @@
         <v>126</v>
       </c>
       <c r="AG57" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AH57" s="1"/>
+      <c r="AH57" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI57" s="1"/>
       <c r="AJ57" s="1"/>
       <c r="AK57" s="1"/>
@@ -10482,7 +10642,7 @@
         <v>65</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="M58" s="1"/>
@@ -10491,28 +10651,28 @@
         <v>84</v>
       </c>
       <c r="P58" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>13.6</v>
       </c>
       <c r="Q58" s="5">
         <v>93.4</v>
       </c>
       <c r="R58" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>93.4</v>
       </c>
       <c r="S58" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>84</v>
       </c>
       <c r="T58" s="23"/>
       <c r="U58" s="23"/>
       <c r="V58" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>13.308823529411764</v>
       </c>
       <c r="W58" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.132352941176471</v>
       </c>
       <c r="X58" s="1">
@@ -10523,18 +10683,18 @@
       </c>
       <c r="Z58" s="1"/>
       <c r="AA58" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>21.482000000000003</v>
       </c>
       <c r="AB58" s="7">
         <v>6</v>
       </c>
       <c r="AC58" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14</v>
       </c>
       <c r="AD58" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>19.32</v>
       </c>
       <c r="AE58" s="1">
@@ -10544,10 +10704,13 @@
         <v>140</v>
       </c>
       <c r="AG58" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.1</v>
       </c>
-      <c r="AH58" s="1"/>
+      <c r="AH58" s="1">
+        <f t="shared" si="5"/>
+        <v>3.1280000000000001</v>
+      </c>
       <c r="AI58" s="1"/>
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
@@ -10600,7 +10763,7 @@
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>248</v>
       </c>
       <c r="M59" s="1"/>
@@ -10609,18 +10772,18 @@
         <v>336</v>
       </c>
       <c r="P59" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>49.6</v>
       </c>
       <c r="Q59" s="5">
         <v>356.4</v>
       </c>
       <c r="R59" s="5">
-        <f t="shared" ref="R59:R60" si="25">T59</f>
+        <f t="shared" ref="R59:R60" si="26">T59</f>
         <v>700</v>
       </c>
       <c r="S59" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>672</v>
       </c>
       <c r="T59" s="23">
@@ -10632,11 +10795,11 @@
         <v>Сети</v>
       </c>
       <c r="V59" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>20.362903225806452</v>
       </c>
       <c r="W59" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6.814516129032258</v>
       </c>
       <c r="X59" s="1">
@@ -10647,18 +10810,18 @@
       </c>
       <c r="Z59" s="1"/>
       <c r="AA59" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>175</v>
       </c>
       <c r="AB59" s="7">
         <v>12</v>
       </c>
       <c r="AC59" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>56</v>
       </c>
       <c r="AD59" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>168</v>
       </c>
       <c r="AE59" s="1">
@@ -10668,10 +10831,13 @@
         <v>70</v>
       </c>
       <c r="AG59" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.8</v>
       </c>
-      <c r="AH59" s="1"/>
+      <c r="AH59" s="1">
+        <f t="shared" si="5"/>
+        <v>12.4</v>
+      </c>
       <c r="AI59" s="1"/>
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
@@ -10722,7 +10888,7 @@
         <v>6</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>206</v>
       </c>
       <c r="M60" s="1"/>
@@ -10731,18 +10897,18 @@
         <v>168</v>
       </c>
       <c r="P60" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>42.4</v>
       </c>
       <c r="Q60" s="5">
         <v>353.6</v>
       </c>
       <c r="R60" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>600</v>
       </c>
       <c r="S60" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>672</v>
       </c>
       <c r="T60" s="23">
@@ -10754,11 +10920,11 @@
         <v>Сети</v>
       </c>
       <c r="V60" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>21.509433962264151</v>
       </c>
       <c r="W60" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.6603773584905666</v>
       </c>
       <c r="X60" s="1">
@@ -10769,18 +10935,18 @@
       </c>
       <c r="Z60" s="1"/>
       <c r="AA60" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>150</v>
       </c>
       <c r="AB60" s="7">
         <v>12</v>
       </c>
       <c r="AC60" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>56</v>
       </c>
       <c r="AD60" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>168</v>
       </c>
       <c r="AE60" s="1">
@@ -10790,10 +10956,13 @@
         <v>70</v>
       </c>
       <c r="AG60" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.8</v>
       </c>
-      <c r="AH60" s="1"/>
+      <c r="AH60" s="1">
+        <f t="shared" si="5"/>
+        <v>10.6</v>
+      </c>
       <c r="AI60" s="1"/>
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
@@ -10844,7 +11013,7 @@
         <v>2</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M61" s="1"/>
@@ -10853,25 +11022,25 @@
         <v>0</v>
       </c>
       <c r="P61" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
       <c r="Q61" s="5"/>
       <c r="R61" s="5"/>
       <c r="S61" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="T61" s="23"/>
       <c r="U61" s="23"/>
       <c r="V61" s="1">
-        <f t="shared" si="17"/>
-        <v>145</v>
-      </c>
-      <c r="W61" s="1">
         <f t="shared" si="18"/>
         <v>145</v>
       </c>
+      <c r="W61" s="1">
+        <f t="shared" si="19"/>
+        <v>145</v>
+      </c>
       <c r="X61" s="1">
         <v>0</v>
       </c>
@@ -10882,20 +11051,20 @@
         <v>167</v>
       </c>
       <c r="AA61" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AB61" s="7">
         <v>6</v>
       </c>
       <c r="AC61" s="9">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AD61" s="1">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AD61" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AE61" s="1">
         <v>14</v>
       </c>
@@ -10903,10 +11072,13 @@
         <v>140</v>
       </c>
       <c r="AG61" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AH61" s="1"/>
+      <c r="AH61" s="1">
+        <f t="shared" si="5"/>
+        <v>7.1999999999999995E-2</v>
+      </c>
       <c r="AI61" s="1"/>
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
@@ -10959,7 +11131,7 @@
         <v>10</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-2</v>
       </c>
       <c r="M62" s="1"/>
@@ -10968,25 +11140,25 @@
         <v>84</v>
       </c>
       <c r="P62" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.6</v>
       </c>
       <c r="Q62" s="5"/>
       <c r="R62" s="5"/>
       <c r="S62" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="T62" s="23"/>
       <c r="U62" s="23"/>
       <c r="V62" s="1">
-        <f t="shared" si="17"/>
-        <v>56.25</v>
-      </c>
-      <c r="W62" s="1">
         <f t="shared" si="18"/>
         <v>56.25</v>
       </c>
+      <c r="W62" s="1">
+        <f t="shared" si="19"/>
+        <v>56.25</v>
+      </c>
       <c r="X62" s="1">
         <v>3.6</v>
       </c>
@@ -10995,20 +11167,20 @@
       </c>
       <c r="Z62" s="1"/>
       <c r="AA62" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AB62" s="7">
         <v>6</v>
       </c>
       <c r="AC62" s="9">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AD62" s="1">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AD62" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AE62" s="1">
         <v>14</v>
       </c>
@@ -11016,10 +11188,13 @@
         <v>140</v>
       </c>
       <c r="AG62" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AH62" s="1"/>
+      <c r="AH62" s="1">
+        <f t="shared" si="5"/>
+        <v>0.28799999999999998</v>
+      </c>
       <c r="AI62" s="1"/>
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
@@ -11066,7 +11241,7 @@
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M63" s="1"/>
@@ -11075,25 +11250,25 @@
         <v>0</v>
       </c>
       <c r="P63" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Q63" s="5"/>
       <c r="R63" s="5"/>
       <c r="S63" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="T63" s="23"/>
       <c r="U63" s="23"/>
       <c r="V63" s="1" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W63" s="1" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="W63" s="1" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X63" s="1">
         <v>1.2</v>
       </c>
@@ -11104,20 +11279,20 @@
         <v>167</v>
       </c>
       <c r="AA63" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AB63" s="7">
         <v>6</v>
       </c>
       <c r="AC63" s="9">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AD63" s="1">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AD63" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AE63" s="1">
         <v>14</v>
       </c>
@@ -11125,10 +11300,13 @@
         <v>140</v>
       </c>
       <c r="AG63" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AH63" s="1"/>
+      <c r="AH63" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI63" s="1"/>
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
@@ -11181,7 +11359,7 @@
         <v>197</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-8</v>
       </c>
       <c r="M64" s="1"/>
@@ -11190,28 +11368,28 @@
         <v>168</v>
       </c>
       <c r="P64" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>37.799999999999997</v>
       </c>
       <c r="Q64" s="5">
         <v>237.19999999999993</v>
       </c>
       <c r="R64" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>237.19999999999993</v>
       </c>
       <c r="S64" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>168</v>
       </c>
       <c r="T64" s="23"/>
       <c r="U64" s="23"/>
       <c r="V64" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>12.169312169312171</v>
       </c>
       <c r="W64" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.7248677248677255</v>
       </c>
       <c r="X64" s="1">
@@ -11222,18 +11400,18 @@
       </c>
       <c r="Z64" s="1"/>
       <c r="AA64" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>71.159999999999982</v>
       </c>
       <c r="AB64" s="7">
         <v>12</v>
       </c>
       <c r="AC64" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14</v>
       </c>
       <c r="AD64" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>50.4</v>
       </c>
       <c r="AE64" s="1">
@@ -11243,10 +11421,13 @@
         <v>70</v>
       </c>
       <c r="AG64" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.2</v>
       </c>
-      <c r="AH64" s="1"/>
+      <c r="AH64" s="1">
+        <f t="shared" si="5"/>
+        <v>11.339999999999998</v>
+      </c>
       <c r="AI64" s="1"/>
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
@@ -11299,7 +11480,7 @@
         <v>123</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="M65" s="1"/>
@@ -11308,28 +11489,28 @@
         <v>168</v>
       </c>
       <c r="P65" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>25.4</v>
       </c>
       <c r="Q65" s="5">
         <v>108.59999999999997</v>
       </c>
       <c r="R65" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>108.59999999999997</v>
       </c>
       <c r="S65" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>168</v>
       </c>
       <c r="T65" s="23"/>
       <c r="U65" s="23"/>
       <c r="V65" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>16.338582677165356</v>
       </c>
       <c r="W65" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9.7244094488188981</v>
       </c>
       <c r="X65" s="1">
@@ -11340,18 +11521,18 @@
       </c>
       <c r="Z65" s="1"/>
       <c r="AA65" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>32.579999999999991</v>
       </c>
       <c r="AB65" s="7">
         <v>12</v>
       </c>
       <c r="AC65" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14</v>
       </c>
       <c r="AD65" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>50.4</v>
       </c>
       <c r="AE65" s="1">
@@ -11361,10 +11542,13 @@
         <v>70</v>
       </c>
       <c r="AG65" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.2</v>
       </c>
-      <c r="AH65" s="1"/>
+      <c r="AH65" s="1">
+        <f t="shared" si="5"/>
+        <v>7.6199999999999992</v>
+      </c>
       <c r="AI65" s="1"/>
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
@@ -11417,7 +11601,7 @@
         <v>157</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-59</v>
       </c>
       <c r="M66" s="1"/>
@@ -11426,7 +11610,7 @@
         <v>196</v>
       </c>
       <c r="P66" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>19.600000000000001</v>
       </c>
       <c r="Q66" s="5">
@@ -11437,17 +11621,17 @@
         <v>110.60000000000002</v>
       </c>
       <c r="S66" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>196</v>
       </c>
       <c r="T66" s="23"/>
       <c r="U66" s="23"/>
       <c r="V66" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>20.357142857142854</v>
       </c>
       <c r="W66" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10.357142857142856</v>
       </c>
       <c r="X66" s="1">
@@ -11458,18 +11642,18 @@
       </c>
       <c r="Z66" s="1"/>
       <c r="AA66" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>33.180000000000007</v>
       </c>
       <c r="AB66" s="7">
         <v>14</v>
       </c>
       <c r="AC66" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14</v>
       </c>
       <c r="AD66" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>58.8</v>
       </c>
       <c r="AE66" s="1">
@@ -11479,10 +11663,13 @@
         <v>70</v>
       </c>
       <c r="AG66" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.2</v>
       </c>
-      <c r="AH66" s="1"/>
+      <c r="AH66" s="1">
+        <f t="shared" si="5"/>
+        <v>5.88</v>
+      </c>
       <c r="AI66" s="1"/>
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
@@ -11533,7 +11720,7 @@
         <v>38</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1</v>
       </c>
       <c r="M67" s="1"/>
@@ -11542,28 +11729,28 @@
         <v>0</v>
       </c>
       <c r="P67" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>7.4</v>
       </c>
       <c r="Q67" s="5">
         <v>61.600000000000009</v>
       </c>
       <c r="R67" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>61.600000000000009</v>
       </c>
       <c r="S67" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>84</v>
       </c>
       <c r="T67" s="23"/>
       <c r="U67" s="23"/>
       <c r="V67" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>17.027027027027025</v>
       </c>
       <c r="W67" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.6756756756756754</v>
       </c>
       <c r="X67" s="1">
@@ -11574,18 +11761,18 @@
       </c>
       <c r="Z67" s="1"/>
       <c r="AA67" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.552000000000001</v>
       </c>
       <c r="AB67" s="7">
         <v>6</v>
       </c>
       <c r="AC67" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14</v>
       </c>
       <c r="AD67" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>18.48</v>
       </c>
       <c r="AE67" s="1">
@@ -11595,10 +11782,13 @@
         <v>140</v>
       </c>
       <c r="AG67" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.1</v>
       </c>
-      <c r="AH67" s="1"/>
+      <c r="AH67" s="1">
+        <f t="shared" si="5"/>
+        <v>1.6280000000000001</v>
+      </c>
       <c r="AI67" s="1"/>
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
@@ -11651,7 +11841,7 @@
         <v>565</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>58</v>
       </c>
       <c r="M68" s="1"/>
@@ -11660,28 +11850,28 @@
         <v>672</v>
       </c>
       <c r="P68" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>124.6</v>
       </c>
       <c r="Q68" s="5">
         <v>1068.3999999999999</v>
       </c>
       <c r="R68" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1068.3999999999999</v>
       </c>
       <c r="S68" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1008</v>
       </c>
       <c r="T68" s="23"/>
       <c r="U68" s="23"/>
       <c r="V68" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>13.515248796147674</v>
       </c>
       <c r="W68" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.4253611556982344</v>
       </c>
       <c r="X68" s="1">
@@ -11692,18 +11882,18 @@
       </c>
       <c r="Z68" s="1"/>
       <c r="AA68" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>267.09999999999997</v>
       </c>
       <c r="AB68" s="7">
         <v>12</v>
       </c>
       <c r="AC68" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>84</v>
       </c>
       <c r="AD68" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>252</v>
       </c>
       <c r="AE68" s="1">
@@ -11713,10 +11903,13 @@
         <v>70</v>
       </c>
       <c r="AG68" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1.2</v>
       </c>
-      <c r="AH68" s="1"/>
+      <c r="AH68" s="1">
+        <f t="shared" si="5"/>
+        <v>31.15</v>
+      </c>
       <c r="AI68" s="1"/>
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
@@ -11769,7 +11962,7 @@
         <v>417</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>54</v>
       </c>
       <c r="M69" s="1"/>
@@ -11778,28 +11971,28 @@
         <v>504</v>
       </c>
       <c r="P69" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>94.2</v>
       </c>
       <c r="Q69" s="5">
         <v>796.8</v>
       </c>
       <c r="R69" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>796.8</v>
       </c>
       <c r="S69" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>840</v>
       </c>
       <c r="T69" s="23"/>
       <c r="U69" s="23"/>
       <c r="V69" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>14.45859872611465</v>
       </c>
       <c r="W69" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.5414012738853504</v>
       </c>
       <c r="X69" s="1">
@@ -11810,18 +12003,18 @@
       </c>
       <c r="Z69" s="1"/>
       <c r="AA69" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>199.2</v>
       </c>
       <c r="AB69" s="7">
         <v>12</v>
       </c>
       <c r="AC69" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>70</v>
       </c>
       <c r="AD69" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>210</v>
       </c>
       <c r="AE69" s="1">
@@ -11831,10 +12024,13 @@
         <v>70</v>
       </c>
       <c r="AG69" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
-      <c r="AH69" s="1"/>
+      <c r="AH69" s="1">
+        <f t="shared" si="5"/>
+        <v>23.55</v>
+      </c>
       <c r="AI69" s="1"/>
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
@@ -11887,7 +12083,7 @@
         <v>31</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L74" si="26">E70-K70</f>
+        <f t="shared" ref="L70:L74" si="27">E70-K70</f>
         <v>-7</v>
       </c>
       <c r="M70" s="1"/>
@@ -11896,23 +12092,23 @@
         <v>84</v>
       </c>
       <c r="P70" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4.8</v>
       </c>
       <c r="Q70" s="5"/>
       <c r="R70" s="5"/>
       <c r="S70" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="T70" s="23"/>
       <c r="U70" s="23"/>
       <c r="V70" s="1">
-        <f t="shared" ref="V70:V74" si="27">(F70+O70+S70)/P70</f>
+        <f t="shared" ref="V70:V74" si="28">(F70+O70+S70)/P70</f>
         <v>18.333333333333336</v>
       </c>
       <c r="W70" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>18.333333333333336</v>
       </c>
       <c r="X70" s="1">
@@ -11923,20 +12119,20 @@
       </c>
       <c r="Z70" s="1"/>
       <c r="AA70" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AB70" s="7">
         <v>6</v>
       </c>
       <c r="AC70" s="9">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AD70" s="1">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AD70" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AE70" s="1">
         <v>14</v>
       </c>
@@ -11944,10 +12140,13 @@
         <v>140</v>
       </c>
       <c r="AG70" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AH70" s="1"/>
+      <c r="AH70" s="1">
+        <f t="shared" si="5"/>
+        <v>0.96</v>
+      </c>
       <c r="AI70" s="1"/>
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
@@ -12000,7 +12199,7 @@
         <v>111</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M71" s="1"/>
@@ -12009,28 +12208,28 @@
         <v>84</v>
       </c>
       <c r="P71" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.2</v>
       </c>
       <c r="Q71" s="5">
         <v>189.8</v>
       </c>
       <c r="R71" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>189.8</v>
       </c>
       <c r="S71" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>168</v>
       </c>
       <c r="T71" s="23"/>
       <c r="U71" s="23"/>
       <c r="V71" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>13.018018018018019</v>
       </c>
       <c r="W71" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.4504504504504503</v>
       </c>
       <c r="X71" s="1">
@@ -12041,18 +12240,18 @@
       </c>
       <c r="Z71" s="1"/>
       <c r="AA71" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>43.654000000000003</v>
       </c>
       <c r="AB71" s="7">
         <v>6</v>
       </c>
       <c r="AC71" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>28</v>
       </c>
       <c r="AD71" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>38.64</v>
       </c>
       <c r="AE71" s="1">
@@ -12062,10 +12261,13 @@
         <v>140</v>
       </c>
       <c r="AG71" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.2</v>
       </c>
-      <c r="AH71" s="1"/>
+      <c r="AH71" s="1">
+        <f t="shared" ref="AH71:AH74" si="29">P71*G71</f>
+        <v>5.1059999999999999</v>
+      </c>
       <c r="AI71" s="1"/>
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
@@ -12116,7 +12318,7 @@
         <v>92</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8</v>
       </c>
       <c r="M72" s="1"/>
@@ -12125,28 +12327,28 @@
         <v>84</v>
       </c>
       <c r="P72" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>20</v>
       </c>
       <c r="Q72" s="5">
         <v>66</v>
       </c>
       <c r="R72" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>66</v>
       </c>
       <c r="S72" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>84</v>
       </c>
       <c r="T72" s="23"/>
       <c r="U72" s="23"/>
       <c r="V72" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>14.9</v>
       </c>
       <c r="W72" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10.7</v>
       </c>
       <c r="X72" s="1">
@@ -12157,18 +12359,18 @@
       </c>
       <c r="Z72" s="1"/>
       <c r="AA72" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15.180000000000001</v>
       </c>
       <c r="AB72" s="7">
         <v>6</v>
       </c>
       <c r="AC72" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14</v>
       </c>
       <c r="AD72" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>19.32</v>
       </c>
       <c r="AE72" s="1">
@@ -12178,10 +12380,13 @@
         <v>140</v>
       </c>
       <c r="AG72" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.1</v>
       </c>
-      <c r="AH72" s="1"/>
+      <c r="AH72" s="1">
+        <f t="shared" si="29"/>
+        <v>4.6000000000000005</v>
+      </c>
       <c r="AI72" s="1"/>
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
@@ -12228,7 +12433,7 @@
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M73" s="1"/>
@@ -12237,23 +12442,23 @@
         <v>0</v>
       </c>
       <c r="P73" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Q73" s="5"/>
       <c r="R73" s="5"/>
       <c r="S73" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="T73" s="23"/>
       <c r="U73" s="23"/>
       <c r="V73" s="1" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W73" s="1" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X73" s="1">
@@ -12266,20 +12471,20 @@
         <v>167</v>
       </c>
       <c r="AA73" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AB73" s="7">
         <v>2.7</v>
       </c>
       <c r="AC73" s="9">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AD73" s="1">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AD73" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AE73" s="1">
         <v>14</v>
       </c>
@@ -12287,10 +12492,13 @@
         <v>126</v>
       </c>
       <c r="AG73" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AH73" s="1"/>
+      <c r="AH73" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AI73" s="1"/>
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
@@ -12343,7 +12551,7 @@
         <v>50</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M74" s="1"/>
@@ -12352,23 +12560,23 @@
         <v>120</v>
       </c>
       <c r="P74" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>10</v>
       </c>
       <c r="Q74" s="5"/>
       <c r="R74" s="5"/>
       <c r="S74" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="T74" s="23"/>
       <c r="U74" s="23"/>
       <c r="V74" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>20.5</v>
       </c>
       <c r="W74" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>20.5</v>
       </c>
       <c r="X74" s="1">
@@ -12379,20 +12587,20 @@
       </c>
       <c r="Z74" s="1"/>
       <c r="AA74" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AB74" s="7">
         <v>5</v>
       </c>
       <c r="AC74" s="9">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AD74" s="1">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AD74" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AE74" s="1">
         <v>12</v>
       </c>
@@ -12400,10 +12608,13 @@
         <v>84</v>
       </c>
       <c r="AG74" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AH74" s="1"/>
+      <c r="AH74" s="1">
+        <f t="shared" si="29"/>
+        <v>10</v>
+      </c>
       <c r="AI74" s="1"/>
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
